--- a/dist/storage_results.xlsx
+++ b/dist/storage_results.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-18_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_sopris_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_storquest_results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_storage_mart_results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_all_hours_results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-06-19_carbondale_results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,16 +429,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -447,10 +452,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5x5 Driveup Hallway</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
+        <is>
+          <t>Driveup Hallway</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>89.00</t>
         </is>
@@ -459,10 +469,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5x5 Indoor Better 2nd floor</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>95.00</t>
         </is>
@@ -471,10 +486,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5x5 Indoor Better 3rd floor</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>95.00</t>
         </is>
@@ -483,10 +503,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5x5 Indoor Good 3rd floor</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>95.00</t>
         </is>
@@ -495,10 +520,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10x5 DriveUp Original Units</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>139.00</t>
         </is>
@@ -507,10 +537,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5x10 DriveUp Original Units</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>143.00</t>
         </is>
@@ -519,10 +554,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5x10 Driveup Hallway</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>Driveup Hallway</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>145.00</t>
         </is>
@@ -531,10 +571,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10x5 Indoor Best 2nd floor</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>Indoor Best 2nd floor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>153.00</t>
         </is>
@@ -543,10 +588,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10x5 Indoor Good 2nd floor</t>
+          <t>10x5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>153.00</t>
         </is>
@@ -555,10 +605,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5x10 Indoor Good 3rd floor</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>159.00</t>
         </is>
@@ -567,10 +622,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10x20 Indoor Good 3rd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>170.00</t>
         </is>
@@ -579,10 +639,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10x21 Indoor Good 3rd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>170.00</t>
         </is>
@@ -591,10 +656,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 3rd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>173.00</t>
         </is>
@@ -603,10 +673,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10x21 Indoor Better 3rd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>173.00</t>
         </is>
@@ -615,10 +690,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8x9 Bins Self Storage</t>
+          <t>8x9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
+        <is>
+          <t>Bins Self Storage</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>174.00</t>
         </is>
@@ -627,10 +707,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15x5 Indoor Good 2nd floor</t>
+          <t>15x5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
@@ -639,10 +724,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 3rd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
+        <is>
+          <t>Indoor Best 3rd floor</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
@@ -651,10 +741,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5x15 DriveUp Original Units</t>
+          <t>5x15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>181.00</t>
         </is>
@@ -663,10 +758,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 2nd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -675,10 +775,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 3rd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -687,10 +792,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10x11 Indoor Good 2nd floor</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -699,10 +809,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10x11 Indoor Good 3rd floor</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>212.00</t>
         </is>
@@ -711,10 +826,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10x10 Indoor Better 2nd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>215.00</t>
         </is>
@@ -723,10 +843,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10x10 Indoor Better 3rd floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
+        <is>
+          <t>Indoor Better 3rd floor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>215.00</t>
         </is>
@@ -735,10 +860,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10x11 Indoor Better 2nd floor</t>
+          <t>10x11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>215.00</t>
         </is>
@@ -747,10 +877,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10x10 Indoor Good 1st floor</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
+        <is>
+          <t>Indoor Good 1st floor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>220.00</t>
         </is>
@@ -759,10 +894,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 2nd floor</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>270.00</t>
         </is>
@@ -771,10 +911,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 3rd floor</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
+        <is>
+          <t>Indoor Good 3rd floor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>270.00</t>
         </is>
@@ -783,10 +928,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10x15 Indoor Good 1st floor</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
+        <is>
+          <t>Indoor Good 1st floor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>309.00</t>
         </is>
@@ -795,10 +945,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10x16 Indoor Good 1st floor</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
+        <is>
+          <t>Indoor Good 1st floor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>320.00</t>
         </is>
@@ -807,10 +962,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10x16 Indoor Better 1st floor</t>
+          <t>10x16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
+        <is>
+          <t>Indoor Better 1st floor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>328.00</t>
         </is>
@@ -819,10 +979,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10x20 Indoor Good 2nd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>340.00</t>
         </is>
@@ -831,10 +996,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10x21 Indoor Good 2nd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
+        <is>
+          <t>Indoor Good 2nd floor</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>340.00</t>
         </is>
@@ -843,10 +1013,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 2nd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>345.00</t>
         </is>
@@ -855,10 +1030,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10x21 Indoor Better 2nd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
+        <is>
+          <t>Indoor Better 2nd floor</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>345.00</t>
         </is>
@@ -867,10 +1047,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 2nd floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
+        <is>
+          <t>Indoor Best 2nd floor</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>350.00</t>
         </is>
@@ -879,10 +1064,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10x21 Indoor Best 2nd floor</t>
+          <t>10x21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
+        <is>
+          <t>Indoor Best 2nd floor</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>350.00</t>
         </is>
@@ -891,10 +1081,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10x20 Indoor Better 1st floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
+        <is>
+          <t>Indoor Better 1st floor</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>410.00</t>
         </is>
@@ -903,10 +1098,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13.5x18.5 1201 Bldg</t>
+          <t>13.5x18.5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
+        <is>
+          <t>1201 Bldg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>410.00</t>
         </is>
@@ -915,10 +1115,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10x20 Indoor Best 1st floor</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
+        <is>
+          <t>Indoor Best 1st floor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>420.00</t>
         </is>
@@ -927,10 +1132,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10x30 DriveUp Original Units</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
+        <is>
+          <t>DriveUp Original Units</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>555.00</t>
         </is>
@@ -939,10 +1149,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10x25 Driveup New</t>
+          <t>10x25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
+        <is>
+          <t>Driveup New</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>599.00</t>
         </is>
@@ -951,10 +1166,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10x30 Driveup New</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
+        <is>
+          <t>Driveup New</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>749.00</t>
         </is>
@@ -971,16 +1191,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -989,228 +1214,234 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5 x 5</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>$88</t>
+          <t>5x5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>88.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5 x 5</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>$101</t>
+          <t>5x5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>101.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5 x 10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$181</t>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>181.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5 x 10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>$190</t>
+          <t>5x10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>190.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9 x 11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$293</t>
+          <t>9x11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>293.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10 x 10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>$228</t>
+          <t>10x10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>228.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10 x 10</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>$239</t>
+          <t>8x15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>273.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8 x 15</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>$273</t>
+          <t>10x13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>233.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10 x 13</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>$233</t>
+          <t>10x15</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10 x 15</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>$259</t>
+          <t>10x15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>319.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10 x 15</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>$319</t>
+          <t>9x18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>376.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9 x 18</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>$376</t>
+          <t>10x17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>384.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10 x 17</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>$384</t>
+          <t>9x19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>389.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9 x 19</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>$389</t>
+          <t>10x18</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>386.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10 x 18</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>$386</t>
+          <t>10x18</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>410.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10 x 18</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>$410</t>
+          <t>10x18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>467.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10 x 18</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>$467</t>
+          <t>10x20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>429.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10 x 20</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>$429</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10 x 20</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>$514</t>
+          <t>10x20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>514.00</t>
         </is>
       </c>
     </row>
@@ -1225,16 +1456,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -1243,70 +1479,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5'X5'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$114.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>114.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5'X10'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$164.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>164.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5'X15'X8' (Indoor, Heated, First Floor Access)</t>
+          <t>5X15X8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$204.00</t>
+          <t>Indoor Heated First Floor Access</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>204.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8'X10'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>8X10X8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$224.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>224.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10'X8'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X8X8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$246.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>246.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4'X5'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+          <t>4X5X8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1315,10 +1581,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5'X5'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1327,10 +1598,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5'X4'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X4X8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1339,10 +1615,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5'X5'X8' (Indoor, Heated, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X5X8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
+        <is>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1351,10 +1632,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5'X8'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X8X8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1363,10 +1649,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5'X10'X8' (Indoor, First Floor Access, Non-Climate Control)</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1375,10 +1666,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5'X10'X8' (Indoor, Heated, First Floor Access, A/C &amp; Heat)</t>
+          <t>5X10X8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>Indoor Heated First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1387,34 +1683,49 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10'X10'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X10X8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$269.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>269.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10'X15'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X15X8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$375.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>375.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10'X14'X8' (Heated, Drive-Up)</t>
+          <t>10X14X8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
+        <is>
+          <t>Heated Drive-Up</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1423,10 +1734,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10'X11'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>10X11X8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1435,70 +1751,100 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X20X8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$449.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>449.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10'X25'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X25X8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$629.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>629.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10'X30'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X30X8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$825.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>825.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>20X20X8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$1101.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1101.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20'X25'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>20X25X8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$1132.00</t>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1132.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>30'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>30X20X8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1507,10 +1853,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>11'X19'X8' (Drive-Up, A/C &amp; Heat)</t>
+          <t>11X19X8</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
+        <is>
+          <t>Drive-Up A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1519,10 +1870,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10'X32'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X32X8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1531,10 +1887,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15'X20'X8' (Indoor, First Floor Access, A/C &amp; Heat)</t>
+          <t>15X20X8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
+        <is>
+          <t>Indoor First Floor Access A/C &amp; Heat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1543,10 +1904,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10'X40'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>10X40X8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1555,10 +1921,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15'X30'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>15X30X8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1567,10 +1938,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15'X40'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>15X40X8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1579,10 +1955,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20'X30'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>20X30X8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1591,10 +1972,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40'X20'X8' (Drive-Up, Non-Climate Control)</t>
+          <t>40X20X8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
+        <is>
+          <t>Drive-Up Non-Climate Control</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1603,118 +1989,168 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8'X18' (Non-Paved)</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>$159.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>159.00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8'X23' (Non-Paved)</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>$169.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>169.00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8'X28' (Non-Paved)</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>$179.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>179.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>8'X23' (Seasonal, Paved)</t>
+          <t>8X23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>$184.00</t>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>184.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8'X33' (Seasonal, Non-Paved)</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>$199.00</t>
+          <t>Seasonal Non-Paved</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8'X38' (Non-Paved)</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>$229.00</t>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>229.00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8'X33' (Seasonal, Paved)</t>
+          <t>8X33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>$244.00</t>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>244.00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10'X28' (Paved)</t>
+          <t>10X28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>$259.00</t>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8'X38' (Seasonal, Paved)</t>
+          <t>8X38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>$259.00</t>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>259.00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10'X23' (Paved)</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
+        <is>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1723,10 +2159,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8'X17' (Non-Paved)</t>
+          <t>8X17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1735,10 +2176,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>8'X21' (Non-Paved)</t>
+          <t>8X21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1747,10 +2193,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10'X18' (Non-Paved)</t>
+          <t>10X18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1759,10 +2210,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10'X33' (Non-Paved)</t>
+          <t>10X33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1771,10 +2227,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10'X23' (Seasonal, Non-Paved)</t>
+          <t>10X23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
+        <is>
+          <t>Seasonal Non-Paved</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1783,10 +2244,15 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8'X18' (Paved)</t>
+          <t>8X18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
+        <is>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1795,10 +2261,15 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>8'X28' (Paved)</t>
+          <t>8X28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
+        <is>
+          <t>Paved</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1807,10 +2278,15 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8'X31' (Non-Paved)</t>
+          <t>8X31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
+        <is>
+          <t>Non-Paved</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1819,10 +2295,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10'X38' (Seasonal, Paved)</t>
+          <t>10X38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
+        <is>
+          <t>Seasonal Paved</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Sold Out</t>
         </is>
@@ -1839,16 +2320,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -1857,276 +2343,391 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Standard (5 x 5 x 4)</t>
+          <t>5x5x4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>$79</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>79.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Standard (5 x 5)</t>
+          <t>5x5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$99</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>99.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5X5CC (5 x 5 x 8)</t>
+          <t>5x5x8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$117</t>
+          <t>5X5CC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>117.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Standard (5 x 10)</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$175</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>175.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5X10CC (5 x 10)</t>
+          <t>5x10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$190</t>
+          <t>5X10CC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>190.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10X10CC (10 x 10)</t>
+          <t>10x10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$270</t>
+          <t>10X10CC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>270.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Standard (10 x 15)</t>
+          <t>10x15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$375</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>375.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Standard (10 x 20)</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$450</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>450.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Heated 10X20CC (10 x 20)</t>
+          <t>10x20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>Heated 10X20CC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>500.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Standard (10 x 25)</t>
+          <t>10x25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>$575</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>575.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Standard (10 x 30)</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>$695</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>695.00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Standard (15 x 30)</t>
+          <t>15x30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>$760</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>760.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Standard (20 x 20)</t>
+          <t>20x20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$750</t>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>750.00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Paved Outside Parking (19 x 9)</t>
+          <t>19x9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>$199</t>
+          <t>Paved Outside Parking</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 10 (10 x 10 x 10)</t>
+          <t>10x10x10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>$299</t>
+          <t>Ultimate 10 x 10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>299.00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ultimate  (10 x 20 x 10)</t>
+          <t>10x20x10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>$579</t>
+          <t xml:space="preserve">Ultimate </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>579.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 30 (10 x 30 x 10)</t>
+          <t>10x30x10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>$650</t>
+          <t>Ultimate 10 x 30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>650.00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 40 (10 x 40 x 10)</t>
+          <t>10x40x10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>$1,300</t>
+          <t>Ultimate 10 x 40</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1,300.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ultimate 20 x 40 (20 x 40 x 10)</t>
+          <t>20x40x10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>$1,737</t>
+          <t>Ultimate 20 x 40</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1,737.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 10 (10 x 10 x 10)</t>
+          <t>10x10x10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>$299</t>
+          <t>Ultimate 10 x 10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>299.00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 20 (10 x 20 x 10)</t>
+          <t>10x20x10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>$579</t>
+          <t>Ultimate 10 x 20</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>579.00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ultimate 10 x 30 (30 x 10)</t>
+          <t>30x10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>$650</t>
+          <t>Ultimate 10 x 30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>650.00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ultimate 20 x 20  (20 x 20 x 10)</t>
+          <t>20x20x10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>$725</t>
+          <t xml:space="preserve">Ultimate 20 x 20 </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>725.00</t>
         </is>
       </c>
     </row>
@@ -2141,16 +2742,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>unit_name</t>
+          <t>unit_size</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>unit_type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
@@ -2162,9 +2768,10 @@
           <t>10X20</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>$365.00</t>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>365.00</t>
         </is>
       </c>
     </row>
@@ -2174,9 +2781,10 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>$199.00</t>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
@@ -2186,9 +2794,10 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>$199.00</t>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>199.00</t>
         </is>
       </c>
     </row>
@@ -2198,9 +2807,10 @@
           <t>10x10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>$260.00</t>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>260.00</t>
         </is>
       </c>
     </row>
@@ -2210,9 +2820,10 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>$240.00</t>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>240.00</t>
         </is>
       </c>
     </row>
@@ -2222,9 +2833,10 @@
           <t>10x15</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>$305.00</t>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>305.00</t>
         </is>
       </c>
     </row>
@@ -2234,9 +2846,10 @@
           <t>10x20</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>$365.00</t>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>365.00</t>
         </is>
       </c>
     </row>
@@ -2246,9 +2859,10 @@
           <t>10x25</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>$405.00</t>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>405.00</t>
         </is>
       </c>
     </row>
@@ -2258,9 +2872,10 @@
           <t>10x30</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>$475.00</t>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>475.00</t>
         </is>
       </c>
     </row>
@@ -2270,9 +2885,10 @@
           <t>10x30</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>$450.00</t>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>450.00</t>
         </is>
       </c>
     </row>
@@ -2282,9 +2898,10 @@
           <t>12x20</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>$385.00</t>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>385.00</t>
         </is>
       </c>
     </row>
@@ -2294,21 +2911,27 @@
           <t>12x20</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>$440.00</t>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>440.00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12x30 (CC)</t>
+          <t>12x30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>$570.00</t>
+          <t>(CC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>570.00</t>
         </is>
       </c>
     </row>
@@ -2318,9 +2941,10 @@
           <t>12x35</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>$470.00</t>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>470.00</t>
         </is>
       </c>
     </row>
@@ -2330,9 +2954,10 @@
           <t>13x25</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>$440.00</t>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>440.00</t>
         </is>
       </c>
     </row>
@@ -2342,9 +2967,10 @@
           <t>15x20</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>$440.00</t>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>440.00</t>
         </is>
       </c>
     </row>
@@ -2354,9 +2980,10 @@
           <t>15x25</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>$530.00</t>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>530.00</t>
         </is>
       </c>
     </row>
@@ -2366,9 +2993,10 @@
           <t>3X2.7</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>$50.00</t>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>50.00</t>
         </is>
       </c>
     </row>
@@ -2378,9 +3006,10 @@
           <t>5X4X4</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>$80.00</t>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>80.00</t>
         </is>
       </c>
     </row>
@@ -2390,9 +3019,10 @@
           <t>5X5X4</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>$85.00</t>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>85.00</t>
         </is>
       </c>
     </row>
@@ -2402,9 +3032,10 @@
           <t>5X5X8</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>$90.00</t>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>90.00</t>
         </is>
       </c>
     </row>
@@ -2414,9 +3045,10 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>$165.00</t>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>165.00</t>
         </is>
       </c>
     </row>
@@ -2426,9 +3058,10 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>$175.00</t>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>175.00</t>
         </is>
       </c>
     </row>
@@ -2438,9 +3071,10 @@
           <t>5x10</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>$175.00</t>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>175.00</t>
         </is>
       </c>
     </row>
@@ -2450,33 +3084,44 @@
           <t>7x25</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>$260.00</t>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>260.00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Outdoor Parking</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>$110.00</t>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>110.00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Outdoor Parking</t>
+          <t>Outdoor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>Parking</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>145.00</t>
         </is>
       </c>
     </row>
